--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -5984,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
         <v>1</v>
@@ -6070,7 +6070,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -6500,7 +6500,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -6758,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
         <v>1</v>
@@ -6973,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J190" t="n">
         <v>1</v>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J196" t="n">
         <v>1</v>
@@ -9209,7 +9209,7 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -9381,7 +9381,7 @@
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -9639,7 +9639,7 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -10413,7 +10413,7 @@
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -10886,7 +10886,7 @@
         <v>0</v>
       </c>
       <c r="I243" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -11058,7 +11058,7 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J247" t="n">
         <v>1</v>
@@ -11144,7 +11144,7 @@
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="J249" t="n">
         <v>1</v>
@@ -11445,7 +11445,7 @@
         <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J256" t="n">
         <v>1</v>
@@ -11786,10 +11786,10 @@
         <v>0.946534</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J264" t="n">
         <v>1</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -13506,10 +13506,10 @@
         <v>0.928386</v>
       </c>
       <c r="H304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I304" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J304" t="n">
         <v>1</v>
@@ -13552,7 +13552,7 @@
         <v>0</v>
       </c>
       <c r="I305" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J305" t="n">
         <v>0</v>
@@ -13638,7 +13638,7 @@
         <v>0</v>
       </c>
       <c r="I307" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J307" t="n">
         <v>0</v>
@@ -13724,7 +13724,7 @@
         <v>0</v>
       </c>
       <c r="I309" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J309" t="n">
         <v>1</v>
@@ -14108,10 +14108,10 @@
         <v>0.234912</v>
       </c>
       <c r="H318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I318" t="n">
-        <v>0.666667</v>
+        <v>0</v>
       </c>
       <c r="J318" t="n">
         <v>1</v>
@@ -14627,7 +14627,7 @@
         <v>0</v>
       </c>
       <c r="I330" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J330" t="n">
         <v>0</v>
@@ -14799,7 +14799,7 @@
         <v>0</v>
       </c>
       <c r="I334" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J334" t="n">
         <v>1</v>
@@ -15527,10 +15527,10 @@
         <v>0.254672</v>
       </c>
       <c r="H351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J351" t="n">
         <v>1</v>
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="I367" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J367" t="n">
         <v>1</v>
@@ -16304,7 +16304,7 @@
         <v>0</v>
       </c>
       <c r="I369" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J369" t="n">
         <v>1</v>
@@ -16562,7 +16562,7 @@
         <v>0</v>
       </c>
       <c r="I375" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J375" t="n">
         <v>1</v>

--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/UNI2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.182823</v>
+        <v>0.104699</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.133639</v>
+        <v>0.066512</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.251525</v>
+        <v>0.105728</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.994584</v>
+        <v>0.999648</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.159644</v>
+        <v>0.148084</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.7601329999999999</v>
+        <v>0.955306</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.123862</v>
+        <v>0.033145</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.180466</v>
+        <v>0.112775</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.164623</v>
+        <v>0.078879</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.144667</v>
+        <v>0.089644</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.212902</v>
+        <v>0.139379</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.231723</v>
+        <v>0.198709</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.180735</v>
+        <v>0.10687</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.126432</v>
+        <v>0.07904700000000001</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.756769</v>
+        <v>0.810873</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.140023</v>
+        <v>0.066346</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.317178</v>
+        <v>0.326711</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.864896</v>
+        <v>0.923085</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.783621</v>
+        <v>0.831298</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.22525</v>
+        <v>0.207787</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.162653</v>
+        <v>0.116431</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.176996</v>
+        <v>0.102273</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.117945</v>
+        <v>0.051268</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.157188</v>
+        <v>0.06672699999999999</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.530527</v>
+        <v>0.608433</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6018,10 +6018,10 @@
         <v>0.21874</v>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.571412</v>
+        <v>0.289033</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.311536</v>
+        <v>0.252603</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.149931</v>
+        <v>0.082953</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.277906</v>
+        <v>0.128648</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.187533</v>
+        <v>0.155536</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.253018</v>
+        <v>0.095412</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.162804</v>
+        <v>0.07797900000000001</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.180059</v>
+        <v>0.101881</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.139594</v>
+        <v>0.103761</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.167492</v>
+        <v>0.099222</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.132301</v>
+        <v>0.07434399999999999</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.235349</v>
+        <v>0.138024</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.18433</v>
+        <v>0.117646</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.236325</v>
+        <v>0.135433</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.316419</v>
+        <v>0.223633</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.252145</v>
+        <v>0.195503</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.233014</v>
+        <v>0.105658</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.488949</v>
+        <v>0.230868</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.135967</v>
+        <v>0.037346</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.459983</v>
+        <v>0.376532</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.220351</v>
+        <v>0.108475</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.7558240000000001</v>
+        <v>0.905411</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.952282</v>
+        <v>0.989492</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.315782</v>
+        <v>0.143112</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7050,10 +7050,10 @@
         <v>0.008827</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.665079</v>
+        <v>0.454752</v>
       </c>
       <c r="H154" t="n">
         <v>1</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.095274</v>
+        <v>0.056161</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.132828</v>
+        <v>0.155571</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.374976</v>
+        <v>0.339691</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.167001</v>
+        <v>0.092032</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.110252</v>
+        <v>0.064192</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.129479</v>
+        <v>0.105333</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.09644899999999999</v>
+        <v>0.06555999999999999</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.197696</v>
+        <v>0.142192</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.205297</v>
+        <v>0.117822</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.207892</v>
+        <v>0.153455</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.156928</v>
+        <v>0.083592</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.234447</v>
+        <v>0.349249</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.170975</v>
+        <v>0.09517399999999999</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7652,10 +7652,10 @@
         <v>0.004413</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.481385</v>
+        <v>0.6221640000000001</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.122409</v>
+        <v>0.08169899999999999</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.140526</v>
+        <v>0.087048</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.17102</v>
+        <v>0.088169</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>0.596241</v>
+        <v>0.723441</v>
       </c>
       <c r="H172" t="n">
         <v>1</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.09750200000000001</v>
+        <v>0.05699</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.094971</v>
+        <v>0.054556</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.142791</v>
+        <v>0.107151</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.210273</v>
+        <v>0.09636500000000001</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.111558</v>
+        <v>0.043683</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.104177</v>
+        <v>0.036891</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.07717</v>
+        <v>0.040987</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.150365</v>
+        <v>0.147756</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.198645</v>
+        <v>0.14296</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.182337</v>
+        <v>0.275039</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.075986</v>
+        <v>0.098166</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.122341</v>
+        <v>0.10881</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.140002</v>
+        <v>0.114101</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.10559</v>
+        <v>0.081604</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.161016</v>
+        <v>0.09392399999999999</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.194926</v>
+        <v>0.117851</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.168528</v>
+        <v>0.10049</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>0.308989</v>
+        <v>0.262919</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>0.594424</v>
+        <v>0.838342</v>
       </c>
       <c r="H191" t="n">
         <v>1</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.381923</v>
+        <v>0.289463</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8727,10 +8727,10 @@
         <v>0.006615</v>
       </c>
       <c r="F193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.513005</v>
+        <v>0.47061</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.203596</v>
+        <v>0.106187</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.159052</v>
+        <v>0.064608</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.344711</v>
+        <v>0.143905</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.804561</v>
+        <v>0.795376</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.794283</v>
+        <v>0.905425</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="G199" t="n">
-        <v>0.409407</v>
+        <v>0.462548</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.308992</v>
+        <v>0.342131</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.26001</v>
+        <v>0.289649</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.236146</v>
+        <v>0.09006500000000001</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.707137</v>
+        <v>0.873595</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9200,10 +9200,10 @@
         <v>0.000355</v>
       </c>
       <c r="F204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>0.498179</v>
+        <v>0.638832</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.310539</v>
+        <v>0.228028</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.770818</v>
+        <v>0.981553</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>0.575086</v>
+        <v>0.540825</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.305385</v>
+        <v>0.102406</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.318318</v>
+        <v>0.117616</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.987182</v>
+        <v>0.997513</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.261103</v>
+        <v>0.089865</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.27074</v>
+        <v>0.067955</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.345971</v>
+        <v>0.146044</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.294104</v>
+        <v>0.084964</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.284088</v>
+        <v>0.087577</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9719,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0.537018</v>
+        <v>0.577528</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.196028</v>
+        <v>0.030508</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0.023909</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.648626</v>
+        <v>0.482717</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.441291</v>
+        <v>0.127886</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.254162</v>
+        <v>0.124072</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>1</v>
       </c>
       <c r="G221" t="n">
-        <v>0.605329</v>
+        <v>0.852326</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="G222" t="n">
-        <v>0.748085</v>
+        <v>0.885738</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.351765</v>
+        <v>0.216476</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.236722</v>
+        <v>0.080247</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.363819</v>
+        <v>0.194535</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.228512</v>
+        <v>0.098749</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.474643</v>
+        <v>0.493764</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.394244</v>
+        <v>0.170087</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.25855</v>
+        <v>0.072923</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.247572</v>
+        <v>0.111622</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.67952</v>
+        <v>0.517107</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>1</v>
       </c>
       <c r="G232" t="n">
-        <v>0.616007</v>
+        <v>0.853481</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0.926453</v>
+        <v>0.974959</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10493,7 +10493,7 @@
         <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>0.815875</v>
+        <v>0.962516</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>0.836538</v>
+        <v>0.9595050000000001</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.336399</v>
+        <v>0.108791</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.189048</v>
+        <v>0.030114</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.296243</v>
+        <v>0.061844</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.226023</v>
+        <v>0.039802</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.223521</v>
+        <v>0.026904</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.311935</v>
+        <v>0.139619</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.166672</v>
+        <v>0.02444</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.448639</v>
+        <v>0.315428</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10923,7 +10923,7 @@
         <v>1</v>
       </c>
       <c r="G244" t="n">
-        <v>0.851519</v>
+        <v>0.886029</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.8226</v>
+        <v>0.833256</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.570001</v>
+        <v>0.851936</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.897324</v>
+        <v>0.997205</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -11095,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.754806</v>
+        <v>0.773661</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.928485</v>
+        <v>0.999741</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.338326</v>
+        <v>0.193239</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>1</v>
       </c>
       <c r="G251" t="n">
-        <v>0.874118</v>
+        <v>0.803162</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.857525</v>
+        <v>0.996929</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.21842</v>
+        <v>0.050656</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.309186</v>
+        <v>0.150762</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11393,10 +11393,10 @@
         <v>0.004714</v>
       </c>
       <c r="F255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G255" t="n">
-        <v>0.408813</v>
+        <v>0.535126</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.729289</v>
+        <v>0.922381</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.747245</v>
+        <v>0.928684</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.916511</v>
+        <v>0.992305</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.770436</v>
+        <v>0.8618980000000001</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.270119</v>
+        <v>0.068173</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>1</v>
       </c>
       <c r="G261" t="n">
-        <v>0.573825</v>
+        <v>0.625793</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="G262" t="n">
-        <v>0.667776</v>
+        <v>0.638558</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.220159</v>
+        <v>0.092088</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.946534</v>
+        <v>0.99744</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.273447</v>
+        <v>0.054892</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.285944</v>
+        <v>0.100793</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.858384</v>
+        <v>0.934541</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0.795892</v>
+        <v>0.912358</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.301468</v>
+        <v>0.096524</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.441537</v>
+        <v>0.236528</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.349695</v>
+        <v>0.072932</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>1</v>
       </c>
       <c r="G272" t="n">
-        <v>0.67333</v>
+        <v>0.666882</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>0.396534</v>
+        <v>0.40926</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12210,10 +12210,10 @@
         <v>0.001564</v>
       </c>
       <c r="F274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>0.528955</v>
+        <v>0.335211</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12253,10 +12253,10 @@
         <v>1.7e-05</v>
       </c>
       <c r="F275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.631931</v>
+        <v>0.341771</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>0.527318</v>
+        <v>0.5222830000000001</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12342,7 +12342,7 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0.340555</v>
+        <v>0.419978</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0.313262</v>
+        <v>0.167966</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.415764</v>
+        <v>0.219269</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.24955</v>
+        <v>0.095206</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.282854</v>
+        <v>0.197409</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.245784</v>
+        <v>0.120707</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.23822</v>
+        <v>0.080445</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.277348</v>
+        <v>0.197108</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12686,7 +12686,7 @@
         <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.309262</v>
+        <v>0.114683</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0.363051</v>
+        <v>0.137521</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
         <v>0</v>
       </c>
       <c r="G287" t="n">
-        <v>0.490189</v>
+        <v>0.292087</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.341556</v>
+        <v>0.109176</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.324197</v>
+        <v>0.080813</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.319352</v>
+        <v>0.120081</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.296949</v>
+        <v>0.072349</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>1</v>
       </c>
       <c r="G292" t="n">
-        <v>0.5399040000000001</v>
+        <v>0.549728</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.459241</v>
+        <v>0.270164</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.23162</v>
+        <v>0.081582</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.189647</v>
+        <v>0.045859</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.940589</v>
+        <v>0.999301</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -13202,7 +13202,7 @@
         <v>0</v>
       </c>
       <c r="G297" t="n">
-        <v>0.360072</v>
+        <v>0.235714</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.263691</v>
+        <v>0.094555</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>0.323887</v>
+        <v>0.156469</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>0.35285</v>
+        <v>0.269551</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.246425</v>
+        <v>0.066548</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0.670728</v>
+        <v>0.889383</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.65424</v>
+        <v>0.86735</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.928386</v>
+        <v>0.9966699999999999</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.292928</v>
+        <v>0.121844</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.343938</v>
+        <v>0.1324</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0.302465</v>
+        <v>0.30605</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.388003</v>
+        <v>0.257161</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.781298</v>
+        <v>0.94109</v>
       </c>
       <c r="H309" t="n">
         <v>0</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.334909</v>
+        <v>0.091696</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.333549</v>
+        <v>0.101287</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.307689</v>
+        <v>0.071771</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.338933</v>
+        <v>0.178434</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.188096</v>
+        <v>0.122723</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.350028</v>
+        <v>0.345651</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.37205</v>
+        <v>0.217636</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.164968</v>
+        <v>0.152001</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0.234912</v>
+        <v>0.135942</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.461654</v>
+        <v>0.331993</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>0</v>
       </c>
       <c r="G320" t="n">
-        <v>0.411487</v>
+        <v>0.474666</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.127499</v>
+        <v>0.110115</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.450698</v>
+        <v>0.239277</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.086284</v>
+        <v>0.087302</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.130008</v>
+        <v>0.125182</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.109252</v>
+        <v>0.09893299999999999</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.21144</v>
+        <v>0.159305</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.288771</v>
+        <v>0.208959</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14532,10 +14532,10 @@
         <v>0.038857</v>
       </c>
       <c r="F328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G328" t="n">
-        <v>0.6038559999999999</v>
+        <v>0.487308</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.123903</v>
+        <v>0.137988</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.10869</v>
+        <v>0.107441</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.9860640000000001</v>
+        <v>0.983914</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.109343</v>
+        <v>0.08265699999999999</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.9914269999999999</v>
+        <v>0.987527</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14793,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="G334" t="n">
-        <v>0.873762</v>
+        <v>0.844761</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.24016</v>
+        <v>0.198943</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14879,7 +14879,7 @@
         <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.190179</v>
+        <v>0.126114</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.08969199999999999</v>
+        <v>0.058232</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.099074</v>
+        <v>0.080683</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.065123</v>
+        <v>0.052803</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.17909</v>
+        <v>0.138233</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.12028</v>
+        <v>0.118049</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.09549199999999999</v>
+        <v>0.07432999999999999</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.064661</v>
+        <v>0.060681</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.035827</v>
+        <v>0.044437</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.216807</v>
+        <v>0.206049</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.165575</v>
+        <v>0.093977</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.096792</v>
+        <v>0.12645</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0.576306</v>
+        <v>0.51454</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15435,10 +15435,10 @@
         <v>0.000557</v>
       </c>
       <c r="F349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>0.634977</v>
+        <v>0.409166</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.971857</v>
+        <v>0.902662</v>
       </c>
       <c r="H350" t="n">
         <v>1</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.254672</v>
+        <v>0.156643</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.229198</v>
+        <v>0.153943</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.219283</v>
+        <v>0.20816</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.246591</v>
+        <v>0.117656</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.086733</v>
+        <v>0.06723</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.06565</v>
+        <v>0.050562</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.108658</v>
+        <v>0.089223</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>0.188327</v>
+        <v>0.09553300000000001</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.057518</v>
+        <v>0.046238</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>0.284309</v>
+        <v>0.329771</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15951,10 +15951,10 @@
         <v>6.2e-05</v>
       </c>
       <c r="F361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.699555</v>
+        <v>0.457882</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.936922</v>
+        <v>0.934298</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.120073</v>
+        <v>0.082354</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.976015</v>
+        <v>0.949974</v>
       </c>
       <c r="H364" t="n">
         <v>1</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.13026</v>
+        <v>0.137598</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.273139</v>
+        <v>0.177226</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0.911528</v>
+        <v>0.834377</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.18396</v>
+        <v>0.155967</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.453508</v>
+        <v>0.351321</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.203451</v>
+        <v>0.19105</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0.968326</v>
+        <v>0.829941</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.168216</v>
+        <v>0.225459</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.212628</v>
+        <v>0.271964</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.102102</v>
+        <v>0.097732</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.175672</v>
+        <v>0.120077</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.189482</v>
+        <v>0.169441</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.190364</v>
+        <v>0.20471</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.314637</v>
+        <v>0.198198</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.173153</v>
+        <v>0.150725</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16768,10 +16768,10 @@
         <v>0.00046</v>
       </c>
       <c r="F380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G380" t="n">
-        <v>0.678536</v>
+        <v>0.226387</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.38846</v>
+        <v>0.148783</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0.357362</v>
+        <v>0.463583</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.050109</v>
+        <v>0.051635</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.152096</v>
+        <v>0.113514</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.042726</v>
+        <v>0.038285</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.078526</v>
+        <v>0.040063</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.16377</v>
+        <v>0.186707</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.152623</v>
+        <v>0.14837</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.078668</v>
+        <v>0.083201</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.180524</v>
+        <v>0.21977</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.206068</v>
+        <v>0.23424</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0.801087</v>
+        <v>0.590434</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.780067</v>
+        <v>0.768496</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.081077</v>
+        <v>0.092117</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17413,10 +17413,10 @@
         <v>0.159944</v>
       </c>
       <c r="F395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G395" t="n">
-        <v>0.629437</v>
+        <v>0.43236</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.17913</v>
+        <v>0.163318</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>0</v>
       </c>
       <c r="G397" t="n">
-        <v>0.347853</v>
+        <v>0.328514</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.200495</v>
+        <v>0.130216</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.151848</v>
+        <v>0.13058</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.15786</v>
+        <v>0.070664</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17671,10 +17671,10 @@
         <v>0.001755</v>
       </c>
       <c r="F401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>0.368633</v>
+        <v>0.5023840000000001</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.135877</v>
+        <v>0.150288</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.964985</v>
+        <v>0.948256</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.09227100000000001</v>
+        <v>0.061625</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.081653</v>
+        <v>0.05096</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.26016</v>
+        <v>0.224398</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>0</v>
       </c>
       <c r="G407" t="n">
-        <v>0.441293</v>
+        <v>0.291397</v>
       </c>
       <c r="H407" t="n">
         <v>1</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.988331</v>
+        <v>0.9823809999999999</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18015,10 +18015,10 @@
         <v>1e-06</v>
       </c>
       <c r="F409" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.579032</v>
+        <v>0.460651</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.074319</v>
+        <v>0.050381</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0.6652169999999999</v>
+        <v>0.57679</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18144,10 +18144,10 @@
         <v>2e-06</v>
       </c>
       <c r="F412" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>0.509486</v>
+        <v>0.369383</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.144314</v>
+        <v>0.109484</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.776562</v>
+        <v>0.718186</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
